--- a/data anak magang.xlsx
+++ b/data anak magang.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://365tsel-my.sharepoint.com/personal/dea_febriawan_telkomsel_co_id/Documents/Dokumen/Backup D/NOS SULAWESI/NON RUTIN SULAWESI/Program 2026/Q3 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\dashboard_magang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{969A8ADF-8546-4F2B-9A23-067B4BD2E686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C13978-8B48-44B7-BBD8-173F9CB7EF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F34038ED-FEA6-47BE-877F-28A55A0A4DBC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F34038ED-FEA6-47BE-877F-28A55A0A4DBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="166">
   <si>
     <t>Budget Type</t>
   </si>
@@ -534,9 +532,6 @@
   </si>
   <si>
     <t>Supporting Event Perkemahan GPDI</t>
-  </si>
-  <si>
-    <t>Sualwesi</t>
   </si>
   <si>
     <t>Supporting Kunker RI-1 Pulau Miangas</t>
@@ -3020,10 +3015,10 @@
         <v>102</v>
       </c>
       <c r="E41" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" t="s">
         <v>165</v>
-      </c>
-      <c r="F41" t="s">
-        <v>166</v>
       </c>
       <c r="H41" t="s">
         <v>23</v>
